--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46332-2025 artfynd.xlsx
+++ b/artfynd/A 46332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129673658</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
